--- a/output/visualizacion_paralela_mamografia_dic_2025.xlsx
+++ b/output/visualizacion_paralela_mamografia_dic_2025.xlsx
@@ -454,7 +454,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -491,7 +491,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>denominador_piv_mujeres_50_69</t>
+          <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="45" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>denominador_piv_mujeres_50_69</t>
+          <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sin denominador PIV directo; no usar como cobertura establecimiento</t>
+          <t>Sin población inscrita y validada directa; no usar como cobertura establecimiento</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sin denominador PIV directo; no usar como cobertura establecimiento</t>
+          <t>Sin población inscrita y validada directa; no usar como cobertura establecimiento</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sin denominador PIV directo; no usar como cobertura establecimiento</t>
+          <t>Sin población inscrita y validada directa; no usar como cobertura establecimiento</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sin denominador PIV directo; no usar como cobertura establecimiento</t>
+          <t>Sin población inscrita y validada directa; no usar como cobertura establecimiento</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Sin denominador PIV directo; no usar como cobertura establecimiento</t>
+          <t>Sin población inscrita y validada directa; no usar como cobertura establecimiento</t>
         </is>
       </c>
     </row>
@@ -16540,13 +16540,13 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>denominador_piv_mujeres_50_69</t>
+          <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REM con numerador P12 sin PIV directa</t>
+          <t>REM con numerador P12 sin población inscrita y validada directa</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -16680,7 +16680,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REM con numerador P12 sin PIV directa</t>
+          <t>REM con numerador P12 sin población inscrita y validada directa</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -16729,7 +16729,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REM con numerador P12 sin PIV directa</t>
+          <t>REM con numerador P12 sin población inscrita y validada directa</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -16778,7 +16778,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REM con numerador P12 sin PIV directa</t>
+          <t>REM con numerador P12 sin población inscrita y validada directa</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -16832,7 +16832,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REM con numerador P12 sin PIV directa</t>
+          <t>REM con numerador P12 sin población inscrita y validada directa</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -16898,7 +16898,7 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -16958,14 +16958,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PIV mujeres 50-69, inscritos 2024, base de pago 2025</t>
+          <t>Población inscrita y validada mujeres 50-69, inscritos 2024, base de pago 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>alias_piv_aplicado</t>
+          <t>alias_denominador_aplicado</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>numerador_mujeres_50_69 / denominador_piv_mujeres_50_69 * 100</t>
+          <t>numerador_mujeres_50_69 / denominador_poblacion_inscrita_validada_mujeres_50_69 * 100</t>
         </is>
       </c>
     </row>

--- a/output/visualizacion_paralela_mamografia_dic_2025.xlsx
+++ b/output/visualizacion_paralela_mamografia_dic_2025.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,22 +59,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -459,42 +447,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ano</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>IdRegion</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>IdComuna</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>comuna_master</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>numerador_mujeres_50_69</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cobertura_mamografia_pct</t>
         </is>
@@ -2094,82 +2082,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ano</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>IdServicio</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>IdComuna</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>comuna_master</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>IdEstablecimiento</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>establecimiento_master</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tipo_establecimiento_master</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>50_54</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>55_59</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>60_64</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>65_69</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>numerador_mujeres_50_69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>cobertura_mamografia_pct</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>advertencia_cobertura_establecimiento</t>
         </is>
@@ -16557,72 +16545,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tipo_control</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>IdServicio</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>IdComuna</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IdEstablecimiento</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>numerador_mujeres_50_69</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>denominador_poblacion_inscrita_validada_mujeres_50_69</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cobertura_mamografia_pct</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>codigo_madre_master</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>servicio_salud_master</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>comuna_master</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>establecimiento_master</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tipo_establecimiento_master</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>estado_funcionamiento_master</t>
         </is>
@@ -16903,12 +16891,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
